--- a/results/metric_tables_noCatGP.xlsx
+++ b/results/metric_tables_noCatGP.xlsx
@@ -14,8 +14,8 @@
     <sheet name="camel_n8" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="camel_n20" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="camel_n32" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="rastrigin_n20" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="rastrigin_n32" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="rastrigin_n80" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="rastrigin_n160" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1222,36 +1222,36 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Separate GPs</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
-        <v>25.0844</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>1.0425</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>168.8003</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>0.6873</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>25.1853</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>1.0471</v>
-      </c>
-      <c r="J21" s="7" t="n">
-        <v>169.5066</v>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>0.6877</v>
+      <c r="D21" s="6" t="n">
+        <v>19.5795</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.8149</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>141.0882</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.6479</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>19.7318</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.8203</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>143.467</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0.6438</v>
       </c>
     </row>
     <row r="22">
@@ -1263,28 +1263,28 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>30.0056</v>
+        <v>18.6779</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>1.2334</v>
+        <v>0.7784</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>414.1258</v>
+        <v>117.4627</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.2427</v>
+        <v>0.7393</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>28.9016</v>
+        <v>18.8462</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>1.2035</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>337.2243</v>
+        <v>120.8453</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.3401</v>
+        <v>0.7258</v>
       </c>
     </row>
     <row r="23">
@@ -1295,35 +1295,35 @@
           <t>H-LVGP</t>
         </is>
       </c>
-      <c r="D23" s="6" t="n">
-        <v>29.9145</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>1.2295</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>403.0743</v>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>0.2583</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>29.9423</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>1.2414</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>367.6812</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>0.2852</v>
+      <c r="D23" s="7" t="n">
+        <v>18.4756</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>114.1084</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>18.6612</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.7776999999999999</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>117.7109</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>0.7373</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="4" t="n">
-        <v>32</v>
+        <v>160</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
@@ -1331,28 +1331,28 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>23.1841</v>
+        <v>19.0177</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0.9554</v>
+        <v>0.7907</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>125.5133</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>0.8306</v>
+        <v>111.88</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.7897999999999999</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>23.1397</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>0.9538</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>124.9595</v>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>0.8264</v>
+        <v>19.6404</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0.8195</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>118.8248</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0.7659</v>
       </c>
     </row>
     <row r="25">
@@ -1364,28 +1364,28 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>27.3503</v>
+        <v>19.5448</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>1.1338</v>
+        <v>0.8134</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>255.0651</v>
+        <v>113.6752</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.51</v>
+        <v>0.7996</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>27.6975</v>
+        <v>19.78</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1.1505</v>
+        <v>0.8245</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>256.1008</v>
+        <v>115.5928</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>0.5103</v>
+        <v>0.7942</v>
       </c>
     </row>
     <row r="26">
@@ -1397,28 +1397,28 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>27.265</v>
+        <v>19.5573</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>1.1304</v>
+        <v>0.8154</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>249.3798</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0.5205</v>
+        <v>113.3507</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>0.803</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>27.5711</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>1.1452</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>249.9733</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>0.5208</v>
+        <v>19.6461</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.8189</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>113.6923</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>0.7991</v>
       </c>
     </row>
   </sheetData>
@@ -5623,7 +5623,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>rastrigin_6d  |  n_train = 20 (5/level)  |  n_rep = 10  |  seed 1</t>
+          <t>rastrigin_6d  |  n_train = 80 (20/level)  |  n_rep = 10  |  seed 1</t>
         </is>
       </c>
     </row>
@@ -5717,41 +5717,41 @@
           <t>level 1</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
-        <v>29.0445</v>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>1.2285</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>163.8643</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>0.7129</v>
+      <c r="B4" s="6" t="n">
+        <v>18.2459</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0.7853</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>138.0866</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0.6182</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>36.6353</v>
+        <v>16.3099</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1.5339</v>
+        <v>0.7027</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>448.4232</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0.3018</v>
-      </c>
-      <c r="J4" s="6" t="n">
-        <v>36.6245</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>1.5332</v>
-      </c>
-      <c r="L4" s="6" t="n">
-        <v>446.5722</v>
+        <v>99.8656</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>0.8037</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>16.2858</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>0.7016</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>99.4629</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.3027</v>
+        <v>0.8027</v>
       </c>
     </row>
     <row r="5">
@@ -5761,40 +5761,40 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>22.9368</v>
+        <v>18.455</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>124.5153</v>
-      </c>
-      <c r="E5" s="14" t="n">
-        <v>0.8193</v>
-      </c>
-      <c r="F5" s="14" t="n">
-        <v>21.3973</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <v>0.8397</v>
+        <v>0.7391</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>122.8669</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.6807</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>17.223</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.6933</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>279.8354</v>
+        <v>102.341</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.2754</v>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>21.4036</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>271.1409</v>
-      </c>
-      <c r="M5" s="6" t="n">
-        <v>0.3018</v>
+        <v>0.7637</v>
+      </c>
+      <c r="J5" s="14" t="n">
+        <v>17.1182</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>100.3561</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>0.7734</v>
       </c>
     </row>
     <row r="6">
@@ -5803,41 +5803,41 @@
           <t>level 3</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
-        <v>24.9504</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>1.012</v>
-      </c>
-      <c r="D6" s="14" t="n">
-        <v>250.2874</v>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>0.4287</v>
+      <c r="B6" s="6" t="n">
+        <v>21.3717</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>176.8916</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0.5439000000000001</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>36.0749</v>
+        <v>20.0496</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.4438</v>
+        <v>0.8066</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>579.3745</v>
+        <v>126.1523</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.1328</v>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>36.0295</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>1.4416</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>568.2441</v>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>0.1445</v>
+        <v>0.6846</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>19.9399</v>
+      </c>
+      <c r="K6" s="14" t="n">
+        <v>0.8018999999999999</v>
+      </c>
+      <c r="L6" s="14" t="n">
+        <v>123.7236</v>
+      </c>
+      <c r="M6" s="14" t="n">
+        <v>0.6934</v>
       </c>
     </row>
     <row r="7">
@@ -5847,40 +5847,40 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>23.4059</v>
+        <v>20.2453</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>1.0306</v>
+        <v>0.8813</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>136.5342</v>
+        <v>126.5079</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>0.7881</v>
+        <v>0.749</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>25.9147</v>
+        <v>21.1292</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1.1164</v>
+        <v>0.9111</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>348.8699</v>
+        <v>141.4919</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.2607</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>25.6006</v>
+        <v>20.5585</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1.103</v>
+        <v>0.8874</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>326.3401</v>
+        <v>132.8912</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.2842</v>
+        <v>0.7266</v>
       </c>
     </row>
     <row r="8">
@@ -5889,47 +5889,47 @@
           <t>Mean</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>25.0844</v>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>1.0425</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>168.8003</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>0.6873</v>
+      <c r="B8" s="6" t="n">
+        <v>19.5795</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.8149</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>141.0882</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.6479</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>30.0056</v>
+        <v>18.6779</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1.2334</v>
+        <v>0.7784</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>414.1258</v>
+        <v>117.4627</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.2427</v>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>29.9145</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>1.2295</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>403.0743</v>
-      </c>
-      <c r="M8" s="6" t="n">
-        <v>0.2583</v>
+        <v>0.7393</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>18.4756</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>114.1084</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.749</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>rastrigin_6d  |  n_train = 20 (5/level)  |  n_rep = 3  |  seed 1</t>
+          <t>rastrigin_6d  |  n_train = 80 (20/level)  |  n_rep = 3  |  seed 1</t>
         </is>
       </c>
     </row>
@@ -6023,41 +6023,41 @@
           <t>level 1</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
-        <v>28.9045</v>
+      <c r="B13" s="6" t="n">
+        <v>18.2622</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>1.2231</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>159.9452</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>0.7295</v>
+        <v>0.7862</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>138.4994</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.6191</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>30.9294</v>
+        <v>16.5766</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.3097</v>
+        <v>0.7133</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>380.6543</v>
+        <v>101.9397</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.292</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>28.916</v>
+        <v>0.7891</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>16.5537</v>
       </c>
       <c r="K13" s="14" t="n">
-        <v>1.2169</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>350.5571</v>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>0.2666</v>
+        <v>0.7121</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>101.4923</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>0.792</v>
       </c>
     </row>
     <row r="14">
@@ -6066,41 +6066,41 @@
           <t>level 2</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
-        <v>23.0135</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>0.9022</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>125.0884</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>0.8203</v>
+      <c r="B14" s="6" t="n">
+        <v>18.9652</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.7571</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>130.0384</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.6719000000000001</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>26.8345</v>
+        <v>17.3925</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1.0629</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>296.2763</v>
+        <v>105.6776</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.3994</v>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>28.623</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>1.1301</v>
-      </c>
-      <c r="L14" s="6" t="n">
-        <v>355.4029</v>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>0.3154</v>
+        <v>0.752</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>17.345</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>104.4806</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>0.7627</v>
       </c>
     </row>
     <row r="15">
@@ -6109,41 +6109,41 @@
           <t>level 3</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
-        <v>24.9389</v>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>1.0119</v>
-      </c>
-      <c r="D15" s="14" t="n">
-        <v>250.4254</v>
-      </c>
-      <c r="E15" s="14" t="n">
-        <v>0.4307</v>
+      <c r="B15" s="6" t="n">
+        <v>21.0469</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0.843</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>172.7821</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.5635</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>27.9184</v>
+        <v>20.0028</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.1379</v>
+        <v>0.8043</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>310.2203</v>
+        <v>127.5805</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.3467</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>33.068</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>1.3426</v>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>422.9975</v>
-      </c>
-      <c r="M15" s="6" t="n">
-        <v>0.2256</v>
+        <v>0.6768</v>
+      </c>
+      <c r="J15" s="14" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="K15" s="14" t="n">
+        <v>0.8033</v>
+      </c>
+      <c r="L15" s="14" t="n">
+        <v>126.464</v>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>0.6816</v>
       </c>
     </row>
     <row r="16">
@@ -6153,40 +6153,40 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>23.8842</v>
+        <v>20.6531</v>
       </c>
       <c r="C16" s="14" t="n">
-        <v>1.0511</v>
+        <v>0.8951</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>142.5675</v>
+        <v>132.5482</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>0.7705</v>
+        <v>0.7207</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>29.924</v>
+        <v>21.413</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.3036</v>
+        <v>0.9253</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>361.7463</v>
+        <v>148.1834</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3223</v>
+        <v>0.6855</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>29.1622</v>
+        <v>20.7662</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>1.276</v>
+        <v>0.8974</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>341.7674</v>
+        <v>138.4069</v>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0.333</v>
+        <v>0.7129</v>
       </c>
     </row>
     <row r="17">
@@ -6195,41 +6195,41 @@
           <t>Mean</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
-        <v>25.1853</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>1.0471</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>169.5066</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0.6877</v>
+      <c r="B17" s="6" t="n">
+        <v>19.7318</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0.8203</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>143.467</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0.6438</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>28.9016</v>
+        <v>18.8462</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.2035</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>337.2243</v>
+        <v>120.8453</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.3401</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>29.9423</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>1.2414</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>367.6812</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>0.2852</v>
+        <v>0.7258</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>18.6612</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>0.7776999999999999</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>117.7109</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.7373</v>
       </c>
     </row>
   </sheetData>
@@ -6272,7 +6272,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>rastrigin_6d  |  n_train = 32 (8/level)  |  n_rep = 10  |  seed 1</t>
+          <t>rastrigin_6d  |  n_train = 160 (40/level)  |  n_rep = 10  |  seed 1</t>
         </is>
       </c>
     </row>
@@ -6366,41 +6366,41 @@
           <t>level 1</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
-        <v>24.3851</v>
-      </c>
-      <c r="C4" s="14" t="n">
-        <v>1.0478</v>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>138.313</v>
-      </c>
-      <c r="E4" s="14" t="n">
-        <v>0.8105</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>25.8229</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>1.1104</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>241.5206</v>
-      </c>
-      <c r="I4" s="6" t="n">
-        <v>0.5165999999999999</v>
+      <c r="B4" s="6" t="n">
+        <v>17.0351</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0.7346</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>122.5307</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0.6504</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>16.866</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>0.7161999999999999</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>92.622</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>0.8447</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>25.7849</v>
+        <v>16.8806</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>1.1089</v>
+        <v>0.7186</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>239.8454</v>
+        <v>93.2256</v>
       </c>
       <c r="M4" s="6" t="n">
-        <v>0.5205</v>
+        <v>0.8398</v>
       </c>
     </row>
     <row r="5">
@@ -6410,40 +6410,40 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>22.6394</v>
+        <v>19.9129</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>0.8884</v>
+        <v>0.8048999999999999</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>119.8691</v>
+        <v>112.1041</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>0.8008</v>
+        <v>0.8457</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>27.7308</v>
+        <v>20.9412</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1.0992</v>
+        <v>0.8395</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>257.9389</v>
+        <v>126.7864</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.4932</v>
+        <v>0.7725</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>27.7007</v>
+        <v>21.2437</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1.098</v>
+        <v>0.8534</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>252.7354</v>
+        <v>127.7988</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>0.5049</v>
+        <v>0.7685999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -6453,40 +6453,40 @@
         </is>
       </c>
       <c r="B6" s="14" t="n">
-        <v>24.7451</v>
+        <v>19.5738</v>
       </c>
       <c r="C6" s="14" t="n">
-        <v>1.0041</v>
+        <v>0.7936</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>139.0865</v>
+        <v>110.8541</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>0.79</v>
+        <v>0.8213</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>27.3341</v>
+        <v>20.1691</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1.1256</v>
+        <v>0.831</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>255.2461</v>
+        <v>119.5869</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.5312</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>27.2987</v>
+        <v>20.1113</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>1.1243</v>
+        <v>0.8285</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>252.5006</v>
+        <v>119.283</v>
       </c>
       <c r="M6" s="6" t="n">
-        <v>0.5352</v>
+        <v>0.791</v>
       </c>
     </row>
     <row r="7">
@@ -6496,40 +6496,40 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>20.967</v>
+        <v>19.5489</v>
       </c>
       <c r="C7" s="14" t="n">
-        <v>0.8812</v>
+        <v>0.8296</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>104.7847</v>
+        <v>102.0311</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.8418</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>28.5133</v>
+        <v>20.2029</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1.1997</v>
+        <v>0.8668</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>265.5548</v>
+        <v>115.7056</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.499</v>
+        <v>0.7871</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>28.2757</v>
+        <v>19.9937</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1.1903</v>
+        <v>0.8609</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>252.4377</v>
+        <v>113.0953</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.5215</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="8">
@@ -6539,46 +6539,46 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>23.1841</v>
+        <v>19.0177</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>0.9554</v>
+        <v>0.7907</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>125.5133</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>0.8306</v>
+        <v>111.88</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0.7897999999999999</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>27.3503</v>
+        <v>19.5448</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1.1338</v>
+        <v>0.8134</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>255.0651</v>
+        <v>113.6752</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.51</v>
+        <v>0.7996</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>27.265</v>
+        <v>19.5573</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>1.1304</v>
+        <v>0.8154</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>249.3798</v>
-      </c>
-      <c r="M8" s="6" t="n">
-        <v>0.5205</v>
+        <v>113.3507</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.803</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>rastrigin_6d  |  n_train = 32 (8/level)  |  n_rep = 3  |  seed 1</t>
+          <t>rastrigin_6d  |  n_train = 160 (40/level)  |  n_rep = 3  |  seed 1</t>
         </is>
       </c>
     </row>
@@ -6672,41 +6672,41 @@
           <t>level 1</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
-        <v>24.1864</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>1.0399</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>135.838</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>0.8145</v>
+      <c r="B13" s="6" t="n">
+        <v>17.1051</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.7386</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>122.9474</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.6523</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>27.2065</v>
+        <v>16.9514</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1.1704</v>
+        <v>0.721</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>254.0033</v>
-      </c>
-      <c r="I13" s="6" t="n">
-        <v>0.501</v>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>27.132</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>1.1677</v>
-      </c>
-      <c r="L13" s="6" t="n">
-        <v>252.0467</v>
+        <v>92.94110000000001</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>0.8438</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>16.9225</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>0.7199</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>92.7315</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>0.5029</v>
+        <v>0.8438</v>
       </c>
     </row>
     <row r="14">
@@ -6716,40 +6716,40 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>22.5954</v>
+        <v>20.171</v>
       </c>
       <c r="C14" s="14" t="n">
-        <v>0.887</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>119.7236</v>
+        <v>114.7543</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>0.8018</v>
+        <v>0.8418</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>27.9545</v>
+        <v>21.169</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>1.1114</v>
+        <v>0.8491</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>257.3008</v>
+        <v>128.7301</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.502</v>
+        <v>0.7617</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>27.8857</v>
+        <v>20.9876</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>1.1083</v>
+        <v>0.8419</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>250.8041</v>
+        <v>126.3124</v>
       </c>
       <c r="M14" s="6" t="n">
-        <v>0.5195</v>
+        <v>0.7665999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -6759,40 +6759,40 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>24.6988</v>
+        <v>19.9313</v>
       </c>
       <c r="C15" s="14" t="n">
-        <v>1.0026</v>
+        <v>0.8048</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>138.7663</v>
+        <v>111.9573</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>0.793</v>
+        <v>0.8096</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>27.616</v>
+        <v>20.0744</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>1.1352</v>
+        <v>0.8276</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>258.9799</v>
+        <v>118.4212</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.5264</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>27.582</v>
+        <v>20.025</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>1.134</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>257.1253</v>
+        <v>117.6459</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0.5283</v>
+        <v>0.7988</v>
       </c>
     </row>
     <row r="16">
@@ -6801,41 +6801,41 @@
           <t>level 4</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>21.078</v>
-      </c>
-      <c r="C16" s="14" t="n">
-        <v>0.8856000000000001</v>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>105.5101</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>0.8965</v>
+      <c r="B16" s="6" t="n">
+        <v>21.3542</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0.9165</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>125.64</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.7598</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>28.0128</v>
+        <v>20.925</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>1.1848</v>
+        <v>0.9002</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>254.1193</v>
+        <v>122.2789</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.5117</v>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>27.6845</v>
-      </c>
-      <c r="K16" s="6" t="n">
-        <v>1.1708</v>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>239.917</v>
-      </c>
-      <c r="M16" s="6" t="n">
-        <v>0.5322</v>
+        <v>0.7734</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>20.6494</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>0.8885</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>118.0794</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>0.7871</v>
       </c>
     </row>
     <row r="17">
@@ -6845,40 +6845,40 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>23.1397</v>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>0.9538</v>
-      </c>
-      <c r="D17" s="7" t="n">
-        <v>124.9595</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0.8264</v>
+        <v>19.6404</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0.8195</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>118.8248</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0.7659</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>27.6975</v>
+        <v>19.78</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>1.1505</v>
+        <v>0.8245</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>256.1008</v>
+        <v>115.5928</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.5103</v>
+        <v>0.7942</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>27.5711</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>1.1452</v>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>249.9733</v>
-      </c>
-      <c r="M17" s="6" t="n">
-        <v>0.5208</v>
+        <v>19.6461</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>0.8189</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>113.6923</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.7991</v>
       </c>
     </row>
   </sheetData>
